--- a/marketer_forms/020_insertion_order_form--marketer_forms.xlsx
+++ b/marketer_forms/020_insertion_order_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'print',_'label':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Print', 'label': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'digital',_'label':_'digital'}</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Digital', 'label': 'Digital'}</t>
+          <t>Digital</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'full_color',_'label':_'full_color'}</t>
+          <t>full_color</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Full Color', 'label': 'Full Color'}</t>
+          <t>Full Color</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'black_&amp;_white',_'label':_'black_&amp;_white'}</t>
+          <t>black_&amp;_white</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Black &amp; White', 'label': 'Black &amp; White'}</t>
+          <t>Black &amp; White</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'billboard',_'label':_'billboard'}</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Billboard', 'label': 'Billboard'}</t>
+          <t>Billboard</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'tv',_'label':_'tv'}</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'TV', 'label': 'TV'}</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'print',_'label':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Print', 'label': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'print',_'label':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Print', 'label': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'digital',_'label':_'digital'}</t>
+          <t>digital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Digital', 'label': 'Digital'}</t>
+          <t>Digital</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'new',_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'New', 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'reorder',_'label':_'reorder'}</t>
+          <t>reorder</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Reorder', 'label': 'Reorder'}</t>
+          <t>Reorder</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'square_foot',_'label':_'square_foot'}</t>
+          <t>square_foot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Square Foot', 'label': 'Square Foot'}</t>
+          <t>Square Foot</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'page_count',_'label':_'page_count'}</t>
+          <t>page_count</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Page Count', 'label': 'Page Count'}</t>
+          <t>Page Count</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'column_inch',_'label':_'column_inch'}</t>
+          <t>column_inch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Column Inch', 'label': 'Column Inch'}</t>
+          <t>Column Inch</t>
         </is>
       </c>
     </row>
